--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/mar-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1980,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2045,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2110,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2175,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2240,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2492,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2557,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2622,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2748,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2813,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2878,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2943,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3008,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3073,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3199,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3264,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3329,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3394,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3459,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3524,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3650,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3715,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3780,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3845,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3910,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3975,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4040,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4105,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4170,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4235,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4300,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4365,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4430,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4495,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4560,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4625,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4690,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4816,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4881,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4946,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5011,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5076,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5141,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5206,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5271,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5336,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5401,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
